--- a/output/pdf_financials_xlsx/WSP.xlsx
+++ b/output/pdf_financials_xlsx/WSP.xlsx
@@ -900,10 +900,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1665,10 +1665,10 @@
         <v>57</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>87.5</v>
+        <v>88.8</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>265.8</v>
@@ -1751,10 +1751,10 @@
         <v>57</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>87.5</v>
+        <v>88.8</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>265.8</v>
@@ -1948,16 +1948,16 @@
         <v>201.5</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>230.8</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>185.1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>254.7</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>255.6</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>927.4</v>
@@ -2034,16 +2034,16 @@
         <v>201.5</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>230.8</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>185.1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>254.7</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>255.6</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>927.4</v>
@@ -2550,16 +2550,16 @@
         <v>692.4</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1091.4</v>
+        <v>860.6</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1114.9</v>
+        <v>929.8</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1584</v>
+        <v>1329.3</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1488.8</v>
+        <v>1233.2</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>1496.6</v>
@@ -5837,22 +5837,22 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-260.7</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-303.2</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>-235.2</v>
+        <v>-576.5</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>-364.5</v>
+        <v>-375.1</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-375.7</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-384.7</v>
       </c>
     </row>
     <row r="125">
@@ -5880,22 +5880,22 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-260.7</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-303.2</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>-235.2</v>
+        <v>-576.5</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-364.5</v>
+        <v>-375.1</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-375.7</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-384.7</v>
       </c>
     </row>
     <row r="126">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -15610,7 +15610,11 @@
           <t>Lease payments (note 17)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -17828,7 +17832,11 @@
           <t>Lease payments (note 18)</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -33048,7 +33056,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">

--- a/output/pdf_financials_xlsx/WSP.xlsx
+++ b/output/pdf_financials_xlsx/WSP.xlsx
@@ -762,40 +762,40 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>914.3</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>1848.5</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>2664.4</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>5886.3</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>6399.9</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>7251.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>7910.3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>9006.5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>10449.6</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>12567.7</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>14038.6</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>15760.1</v>
       </c>
     </row>
     <row r="10">
@@ -805,40 +805,40 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>914.3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>1848.5</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>2664.4</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>5886.3</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>6399.9</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>7251.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>7910.3</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>9006.5</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>10449.6</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>12567.7</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>14038.6</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>15760.1</v>
       </c>
     </row>
     <row r="11">
@@ -863,31 +863,31 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>6379.6</v>
+        <v>493.3</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>6942.2</v>
+        <v>542.3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>7908.1</v>
+        <v>398.1</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>8916.1</v>
+        <v>487.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>10279.1</v>
+        <v>724.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>11932.9</v>
+        <v>749.1</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>14437.2</v>
+        <v>947.5</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>16166.8</v>
+        <v>1268.6</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>18285</v>
+        <v>1532.6</v>
       </c>
     </row>
     <row r="12">
@@ -940,40 +940,40 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>-8.4</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>-12.5</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-37.2</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-36.9</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-68.8</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-102</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-79.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-161.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-202.6</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-340.6</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-222.3</v>
       </c>
     </row>
     <row r="14">
@@ -1662,40 +1662,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>57</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>95.2</v>
+        <v>107.7</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>88.8</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>265.8</v>
+        <v>303</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>315.4</v>
+        <v>352.3</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>329.3</v>
+        <v>398.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>385.8</v>
+        <v>487.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>645.1</v>
+        <v>724.6</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>587.5</v>
+        <v>749.1</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>744.9</v>
+        <v>947.5</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>928</v>
+        <v>1268.6</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1310.3</v>
+        <v>1532.6</v>
       </c>
     </row>
     <row r="28">
@@ -1705,40 +1705,40 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>2037.6</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>58.7</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>159.5</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>168.8</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>194.4</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>453.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>518.5</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>576.5</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>673.2</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>685.3</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>751.5</v>
       </c>
     </row>
     <row r="29">
@@ -1748,40 +1748,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>57</v>
+        <v>2103</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>95.2</v>
+        <v>166.4</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>88.8</v>
+        <v>166.3</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>265.8</v>
+        <v>462.5</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>315.4</v>
+        <v>521.1</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>329.3</v>
+        <v>592.5</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>385.8</v>
+        <v>941.2</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>645.1</v>
+        <v>1243.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>587.5</v>
+        <v>1325.6</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>744.9</v>
+        <v>1620.7</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>928</v>
+        <v>1953.9</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1310.3</v>
+        <v>2284.1</v>
       </c>
     </row>
     <row r="30">
@@ -1806,31 +1806,31 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>4.16640541726754</v>
+        <v>7.249670825757101</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>4.54322837140964</v>
+        <v>7.506266025179338</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>4.164084925582631</v>
+        <v>7.492318003060154</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>4.327003959130113</v>
+        <v>10.55618487903904</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>6.275841270150111</v>
+        <v>12.09347121829732</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>4.923363138884931</v>
+        <v>11.10878327983977</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>5.159587731693127</v>
+        <v>11.22586097027124</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>5.740158844050771</v>
+        <v>12.08587970408492</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>7.165983046212743</v>
+        <v>12.49165983046213</v>
       </c>
     </row>
     <row r="31">
@@ -5268,22 +5268,22 @@
         <v>-98.09999999999999</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-122.4</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-100.7</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-130.9</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-160.3</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-148.3</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-141.1</v>
       </c>
     </row>
     <row r="112">
@@ -5293,40 +5293,40 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="113">
@@ -5351,25 +5351,25 @@
         <v>0</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0</v>
+        <v>-556.7</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>0</v>
+        <v>-220.9</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>0</v>
+        <v>-1244.9</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>0</v>
+        <v>-2556.7</v>
       </c>
       <c r="K113" s="3" t="n">
-        <v>0</v>
+        <v>-354.3</v>
       </c>
       <c r="L113" s="3" t="n">
-        <v>0</v>
+        <v>-2340</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>0</v>
+        <v>-473.7</v>
       </c>
     </row>
     <row r="114">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>401.1</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -5659,28 +5659,28 @@
         <v>0</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>308.5</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0</v>
+        <v>883.5</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L120" s="3" t="n">
-        <v>0</v>
+        <v>1115.8</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>0</v>
+        <v>949</v>
       </c>
     </row>
     <row r="121">
@@ -5908,13 +5908,13 @@
         <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="F126" s="3" t="n">
         <v>0</v>
@@ -5923,16 +5923,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0</v>
+        <v>-6.2</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="L126" s="3" t="n">
         <v>0</v>
@@ -6145,30 +6145,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I130" s="3" t="n">
+        <v>434.7</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>926.3</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>491</v>
+      </c>
+      <c r="L130" s="3" t="n">
+        <v>361.9</v>
+      </c>
+      <c r="M130" s="3" t="n">
+        <v>619.3</v>
       </c>
     </row>
     <row r="131">
@@ -6298,30 +6288,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I133" s="3" t="n">
+        <v>926.3</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>491</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>361.9</v>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>619.3</v>
+      </c>
+      <c r="M133" s="3" t="n">
+        <v>1545.1</v>
       </c>
     </row>
     <row r="134">
@@ -6349,22 +6329,22 @@
         <v>-98.09999999999999</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-122.4</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-100.7</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-130.9</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-160.3</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-148.3</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-141.1</v>
       </c>
     </row>
     <row r="135">
@@ -6396,22 +6376,22 @@
         <v>571.6</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>814.3</v>
+        <v>691.9</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>1060.1</v>
+        <v>959.3999999999999</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>814.8</v>
+        <v>683.9</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>986.3</v>
+        <v>826</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>1381.9</v>
+        <v>1233.6</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>2246</v>
+        <v>2104.9</v>
       </c>
     </row>
   </sheetData>
@@ -15390,7 +15370,11 @@
           <t>Issuance of common shares, net of issuance costs (note 25)</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -15884,7 +15868,11 @@
           <t>Net disbursements related to business acquisitions and disposals of businesses</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -16032,7 +16020,11 @@
           <t>Additions to property and equipment, excluding business acquisitions</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -16096,7 +16088,11 @@
           <t>Additions to identifiable intangible assets, excluding business acquisitions</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -16160,7 +16156,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -16506,7 +16506,11 @@
           <t>Cash and cash equivalents, net of bank overdraft - beginning of the year</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -16574,7 +16578,11 @@
           <t>Cash and cash equivalents, net of bank overdraft - end of the year (note 28)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -16792,7 +16800,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -17758,7 +17770,11 @@
           <t>Issuance of common shares, net of issuance costs (note 26)</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -18064,7 +18080,11 @@
           <t>Net disbursements related to business acquisitions (note 5)</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -18586,7 +18606,11 @@
           <t>Cash and cash equivalents, net of bank overdraft - end of the year (note 29)</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -18808,7 +18832,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -18880,7 +18908,11 @@
           <t>Dividends paid to a non-controlling interest</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -19030,7 +19062,11 @@
           <t>Net disbursements related to business acquisitions</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -20450,7 +20486,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -20524,7 +20564,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -21642,7 +21686,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -21718,7 +21766,11 @@
           <t>Dividends paid to a non-controlling interest</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -22020,7 +22072,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -22094,7 +22150,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -23820,7 +23880,11 @@
           <t>Issuance of common shares, net of issuance costs (note 17) 1,187.1</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -23896,7 +23960,11 @@
           <t>Dividends paid to a non-controlling interest</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -24196,7 +24264,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -24270,7 +24342,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -26142,7 +26218,11 @@
           <t>Issuance of common shares, net of issuance costs (note 17)</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E270" s="5" t="n">
         <v>401.1</v>
       </c>
@@ -26218,7 +26298,11 @@
           <t>Dividends paid to a non-controlling interest</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -26520,7 +26604,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E275" s="5" t="n">
         <v>1.4</v>
       </c>
@@ -26594,7 +26682,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E276" s="5" t="n">
         <v>-3</v>
       </c>
@@ -27258,7 +27350,11 @@
           <t>Personnel costs</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -27316,7 +27412,11 @@
           <t>Subconsultants and direct costs</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -27372,7 +27472,11 @@
           <t>Other operational costs</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -27428,7 +27532,11 @@
           <t>Depreciation of right-of-use assets (note 17)</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -27494,7 +27602,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -27562,7 +27670,11 @@
           <t>Depreciation of property and equipment (note 19)</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -27886,7 +27998,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -27948,7 +28060,11 @@
           <t>Net financing expense (note 11)</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -28916,7 +29032,11 @@
           <t>Personnel costs (note 11)</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -28986,7 +29106,11 @@
           <t>Depreciation of right-of-use assets (note 18)</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -29058,7 +29182,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -29126,7 +29250,11 @@
           <t>Depreciation of property and equipment (note 20)</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -29338,7 +29466,11 @@
           <t>Net financing expense (note 12)</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -29556,7 +29688,11 @@
           <t>Depreciation of property and equipment (note 18)</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -29912,7 +30048,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -30050,7 +30190,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -30120,7 +30264,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -30394,7 +30538,11 @@
           <t>Net finance expenses (note 22)</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -30900,7 +31048,11 @@
           <t>Net finance expenses (note 20)</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -31048,7 +31200,11 @@
           <t>Personnel costs</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -31122,7 +31278,11 @@
           <t>Subconsultants and direct costs</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -31196,7 +31356,11 @@
           <t>Other operational costs</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -31344,7 +31508,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -31420,7 +31588,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -33206,7 +33374,11 @@
           <t>Personnel costs</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E370" s="5" t="n">
         <v>753.5</v>
       </c>
@@ -33280,7 +33452,11 @@
           <t>Other operational costs</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E371" s="5" t="n">
         <v>160.8</v>
       </c>
@@ -33354,7 +33530,11 @@
           <t>Depreciation of property, plant and equipment 24.7</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E372" s="5" t="n">
         <v>2013</v>
       </c>
@@ -33430,7 +33610,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E373" s="5" t="n">
@@ -33654,7 +33834,11 @@
           <t>Net finance expenses (note 19)</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E376" s="5" t="n">
         <v>8.4</v>
       </c>

--- a/output/pdf_financials_xlsx/WSP.xlsx
+++ b/output/pdf_financials_xlsx/WSP.xlsx
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>421.6</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>423.8</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
@@ -2083,25 +2083,25 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>1555.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>1547.9</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>1615.2</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>2232.6</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>2364.2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0</v>
+        <v>2913.1</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0</v>
+        <v>2598.9</v>
       </c>
     </row>
     <row r="38">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>466.7</v>
+        <v>888.3</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>483.3</v>
+        <v>907.1</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>1234.1</v>
@@ -2255,25 +2255,25 @@
         <v>1554.7</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1758.6</v>
+        <v>3313.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1767.8</v>
+        <v>3315.7</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1916.8</v>
+        <v>3532</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>2625.8</v>
+        <v>4858.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>2726.4</v>
+        <v>5090.6</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>3390.7</v>
+        <v>6303.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>3083.2</v>
+        <v>5682.1</v>
       </c>
     </row>
     <row r="42">
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>215.7</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>210.2</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>692.4</v>
@@ -2556,25 +2556,25 @@
         <v>929.8</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1329.3</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1233.2</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1496.6</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1912.8</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2312.7</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2994.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2786.2</v>
+        <v>187.3</v>
       </c>
     </row>
     <row r="49">
@@ -2909,40 +2909,40 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>125.8</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>146.1</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>293.6</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>661.9</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>773.9</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>805.7</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>924.2</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>1029.7</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>1191.3</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>1362</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>1510.6</v>
       </c>
     </row>
     <row r="57">
@@ -2952,40 +2952,40 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0</v>
+        <v>37.7</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>58.7</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>91.2</v>
       </c>
       <c r="E57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>346.5</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>423.3</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>560.6</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>630.8</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>868.6</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>973</v>
       </c>
     </row>
     <row r="58">
@@ -3256,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>315.1</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>0</v>
@@ -3268,25 +3268,25 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>737.7</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>608.4</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>765.7</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>1038.8</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>1107.7</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>871.3</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>783.8</v>
       </c>
     </row>
     <row r="65">
@@ -3397,25 +3397,25 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>275.7</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>343.7</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>465.5</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>587</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>525.6</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>996.5</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>906.9</v>
       </c>
     </row>
     <row r="68">
@@ -6362,15 +6362,11 @@
       <c r="D135" s="3" t="n">
         <v>94.59999999999998</v>
       </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E135" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>315.7</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>571.6</v>
@@ -19890,7 +19886,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -21316,7 +21316,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
